--- a/demo-knowledge-files/demo-fixtures.xlsx
+++ b/demo-knowledge-files/demo-fixtures.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>治具编号</t>
   </si>
@@ -118,7 +118,7 @@
     <t>后段 B2 插接工位</t>
   </si>
   <si>
-    <t>按孔位图逐孔插接，红灯亮起禁止流转</t>
+    <t>按孔位图逐孔插接，防错灯亮起禁止流转</t>
   </si>
   <si>
     <t>防错探针回弹顺畅，导通测试全绿</t>
@@ -128,6 +128,36 @@
   </si>
   <si>
     <t>孔位图,32P,插接</t>
+  </si>
+  <si>
+    <t>FIX-HV-4821A-BOARD</t>
+  </si>
+  <si>
+    <t>后段导通测试台定位板</t>
+  </si>
+  <si>
+    <t>测试定位</t>
+  </si>
+  <si>
+    <t>后段 B3 导通测试</t>
+  </si>
+  <si>
+    <t>产品按定位销方向放置后锁紧压板</t>
+  </si>
+  <si>
+    <t>定位板无变形，测试针无弯折</t>
+  </si>
+  <si>
+    <t>每班点检</t>
+  </si>
+  <si>
+    <t>pending_review</t>
+  </si>
+  <si>
+    <t>导通测试,定位板,复核</t>
+  </si>
+  <si>
+    <t>V2.4 演示用待复核治具</t>
   </si>
 </sst>
 </file>
@@ -514,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="16" customWidth="1"/>
@@ -661,6 +691,53 @@
         <v>29</v>
       </c>
     </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
